--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/151.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/151.xlsx
@@ -426,13 +426,13 @@
         <v>-12.55394580920908</v>
       </c>
       <c r="E2">
-        <v>-7.385721287991579</v>
+        <v>-10.03274114274712</v>
       </c>
       <c r="F2">
-        <v>-1.162143842102739</v>
+        <v>-2.103866058012328</v>
       </c>
       <c r="G2">
-        <v>-9.576018966653384</v>
+        <v>-10.92677120485912</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.32238515599982</v>
       </c>
       <c r="E3">
-        <v>-8.339743964135508</v>
+        <v>-10.98314103968491</v>
       </c>
       <c r="F3">
-        <v>-1.008321653947936</v>
+        <v>-1.870807103643302</v>
       </c>
       <c r="G3">
-        <v>-9.213229523186811</v>
+        <v>-9.778293299102854</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.05515243111454</v>
       </c>
       <c r="E4">
-        <v>-9.418272504646326</v>
+        <v>-10.74810871021281</v>
       </c>
       <c r="F4">
-        <v>-1.174357382122608</v>
+        <v>-1.915100190686312</v>
       </c>
       <c r="G4">
-        <v>-8.381815805908706</v>
+        <v>-10.18847982305517</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.74496511546353</v>
       </c>
       <c r="E5">
-        <v>-9.916658240034495</v>
+        <v>-13.17960037304729</v>
       </c>
       <c r="F5">
-        <v>-0.9554322111959205</v>
+        <v>-1.880246782752278</v>
       </c>
       <c r="G5">
-        <v>-7.659103851412571</v>
+        <v>-10.24424265211866</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.38678906989587</v>
       </c>
       <c r="E6">
-        <v>-10.7955082476511</v>
+        <v>-14.16943875011788</v>
       </c>
       <c r="F6">
-        <v>-0.6944612319202311</v>
+        <v>-1.619609965424747</v>
       </c>
       <c r="G6">
-        <v>-8.117952084246635</v>
+        <v>-9.028577224642882</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.96265343033258</v>
       </c>
       <c r="E7">
-        <v>-11.37659750384135</v>
+        <v>-14.61555231003551</v>
       </c>
       <c r="F7">
-        <v>-0.7694869241053017</v>
+        <v>-1.895378300921345</v>
       </c>
       <c r="G7">
-        <v>-7.9364183196007</v>
+        <v>-9.443040973431939</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.47557750200729</v>
       </c>
       <c r="E8">
-        <v>-11.77124948513581</v>
+        <v>-15.88114305485518</v>
       </c>
       <c r="F8">
-        <v>-0.3364732201176789</v>
+        <v>-1.686417015761644</v>
       </c>
       <c r="G8">
-        <v>-7.766246347245543</v>
+        <v>-8.659752656658219</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-9.913512094835227</v>
       </c>
       <c r="E9">
-        <v>-11.77711385897575</v>
+        <v>-15.35940397900945</v>
       </c>
       <c r="F9">
-        <v>-0.2361209029329006</v>
+        <v>-1.379292094992303</v>
       </c>
       <c r="G9">
-        <v>-7.258411972066883</v>
+        <v>-9.590135132832836</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.289390882892169</v>
       </c>
       <c r="E10">
-        <v>-12.86663300590318</v>
+        <v>-15.00519579907749</v>
       </c>
       <c r="F10">
-        <v>-0.246369855764667</v>
+        <v>-0.9911748700014733</v>
       </c>
       <c r="G10">
-        <v>-6.897953152659958</v>
+        <v>-9.109410815075268</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-8.602119537750063</v>
       </c>
       <c r="E11">
-        <v>-14.11739299834773</v>
+        <v>-15.6074511427796</v>
       </c>
       <c r="F11">
-        <v>0.2800682438806443</v>
+        <v>-1.334984754596054</v>
       </c>
       <c r="G11">
-        <v>-6.894010292922685</v>
+        <v>-9.075001004740082</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.879369855627096</v>
       </c>
       <c r="E12">
-        <v>-14.2235857138276</v>
+        <v>-17.37166763210984</v>
       </c>
       <c r="F12">
-        <v>0.4611349248987517</v>
+        <v>-0.8687924116799746</v>
       </c>
       <c r="G12">
-        <v>-6.429011066476654</v>
+        <v>-8.58066703427057</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.133928600499623</v>
       </c>
       <c r="E13">
-        <v>-14.6040907423221</v>
+        <v>-17.19207288143964</v>
       </c>
       <c r="F13">
-        <v>0.4019747985745534</v>
+        <v>-0.8783049412610616</v>
       </c>
       <c r="G13">
-        <v>-6.403632424372602</v>
+        <v>-7.334316160191293</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.402660892407167</v>
       </c>
       <c r="E14">
-        <v>-15.84046377284427</v>
+        <v>-18.68895996467507</v>
       </c>
       <c r="F14">
-        <v>0.6065167523772198</v>
+        <v>-0.3612795977241647</v>
       </c>
       <c r="G14">
-        <v>-5.697754593943659</v>
+        <v>-7.994756753093737</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.704237077497657</v>
       </c>
       <c r="E15">
-        <v>-16.41641321103582</v>
+        <v>-20.48553240079012</v>
       </c>
       <c r="F15">
-        <v>1.33206469453524</v>
+        <v>-0.05617548570292429</v>
       </c>
       <c r="G15">
-        <v>-5.323364998907481</v>
+        <v>-7.269849906905065</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.072163904079313</v>
       </c>
       <c r="E16">
-        <v>-17.10466427614358</v>
+        <v>-21.47038945645228</v>
       </c>
       <c r="F16">
-        <v>1.342776881347273</v>
+        <v>0.1249798828464478</v>
       </c>
       <c r="G16">
-        <v>-5.873352550437682</v>
+        <v>-6.51424437193073</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.522539810276093</v>
       </c>
       <c r="E17">
-        <v>-18.60617493134085</v>
+        <v>-19.54670728341593</v>
       </c>
       <c r="F17">
-        <v>1.599158280880018</v>
+        <v>-0.1441836071298098</v>
       </c>
       <c r="G17">
-        <v>-4.660014436476017</v>
+        <v>-6.343887009025375</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.077719239902673</v>
       </c>
       <c r="E18">
-        <v>-18.86506326188536</v>
+        <v>-22.29147877810104</v>
       </c>
       <c r="F18">
-        <v>2.236846969967205</v>
+        <v>0.6915094977411087</v>
       </c>
       <c r="G18">
-        <v>-4.935580936619411</v>
+        <v>-5.804893779231093</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.747155345425513</v>
       </c>
       <c r="E19">
-        <v>-19.57004250997746</v>
+        <v>-21.94898576042693</v>
       </c>
       <c r="F19">
-        <v>2.176355738821079</v>
+        <v>0.7936221040508979</v>
       </c>
       <c r="G19">
-        <v>-4.440846390139646</v>
+        <v>-6.579683925605504</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.541171886412211</v>
       </c>
       <c r="E20">
-        <v>-20.89718427350938</v>
+        <v>-24.36354998742073</v>
       </c>
       <c r="F20">
-        <v>2.731324300533033</v>
+        <v>1.045786094730828</v>
       </c>
       <c r="G20">
-        <v>-4.046070455672636</v>
+        <v>-4.674617252849742</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.464336759339792</v>
       </c>
       <c r="E21">
-        <v>-20.67642116563545</v>
+        <v>-24.25187328991757</v>
       </c>
       <c r="F21">
-        <v>3.28084966501362</v>
+        <v>1.322250468977262</v>
       </c>
       <c r="G21">
-        <v>-4.411716899939599</v>
+        <v>-4.802933997951894</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.516561172129179</v>
       </c>
       <c r="E22">
-        <v>-21.75753093633064</v>
+        <v>-24.8434550203836</v>
       </c>
       <c r="F22">
-        <v>3.357909627447073</v>
+        <v>1.487423077428019</v>
       </c>
       <c r="G22">
-        <v>-4.182954892630422</v>
+        <v>-5.096728361834515</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.696135293832494</v>
       </c>
       <c r="E23">
-        <v>-22.66716098177738</v>
+        <v>-25.3602218317689</v>
       </c>
       <c r="F23">
-        <v>3.498729590036117</v>
+        <v>1.621803691764887</v>
       </c>
       <c r="G23">
-        <v>-3.642889046081416</v>
+        <v>-5.595048229133311</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.989012506356604</v>
       </c>
       <c r="E24">
-        <v>-22.38779489177018</v>
+        <v>-24.99455208412353</v>
       </c>
       <c r="F24">
-        <v>4.193620153083061</v>
+        <v>1.88815610374124</v>
       </c>
       <c r="G24">
-        <v>-3.299270971832763</v>
+        <v>-4.811061387250804</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.383493269013749</v>
       </c>
       <c r="E25">
-        <v>-23.17100352834479</v>
+        <v>-24.89044699516119</v>
       </c>
       <c r="F25">
-        <v>3.996860530148864</v>
+        <v>1.970622838170003</v>
       </c>
       <c r="G25">
-        <v>-3.996511588949747</v>
+        <v>-5.316445958730404</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.851302784563422</v>
       </c>
       <c r="E26">
-        <v>-23.17389722323569</v>
+        <v>-25.98680866631422</v>
       </c>
       <c r="F26">
-        <v>3.689068869189123</v>
+        <v>2.196381700121811</v>
       </c>
       <c r="G26">
-        <v>-3.05363511390992</v>
+        <v>-4.975552463460572</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.374419380222307</v>
       </c>
       <c r="E27">
-        <v>-23.12676486576386</v>
+        <v>-25.59402241631091</v>
       </c>
       <c r="F27">
-        <v>3.919287446998809</v>
+        <v>1.731511751645124</v>
       </c>
       <c r="G27">
-        <v>-3.280632600446666</v>
+        <v>-5.278166120659812</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.918599650259697</v>
       </c>
       <c r="E28">
-        <v>-22.93769654746961</v>
+        <v>-25.58374730878751</v>
       </c>
       <c r="F28">
-        <v>3.639725343981776</v>
+        <v>1.893585047619366</v>
       </c>
       <c r="G28">
-        <v>-3.087783391147502</v>
+        <v>-4.659756213923954</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-6.463564377559622</v>
       </c>
       <c r="E29">
-        <v>-23.45400598298014</v>
+        <v>-25.76645312110098</v>
       </c>
       <c r="F29">
-        <v>3.586047215683871</v>
+        <v>1.66077235952019</v>
       </c>
       <c r="G29">
-        <v>-3.876318922600967</v>
+        <v>-4.135233378681827</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.97528067604695</v>
       </c>
       <c r="E30">
-        <v>-22.60246267362979</v>
+        <v>-24.86098474326729</v>
       </c>
       <c r="F30">
-        <v>3.643337777174893</v>
+        <v>1.969238679199909</v>
       </c>
       <c r="G30">
-        <v>-3.894914256895053</v>
+        <v>-4.794482175190134</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.437895846515755</v>
       </c>
       <c r="E31">
-        <v>-20.71866729965301</v>
+        <v>-25.12189730169322</v>
       </c>
       <c r="F31">
-        <v>3.761181334342742</v>
+        <v>1.741311723849863</v>
       </c>
       <c r="G31">
-        <v>-2.866681986216197</v>
+        <v>-4.660782483041128</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.826177677953527</v>
       </c>
       <c r="E32">
-        <v>-22.55870855776768</v>
+        <v>-24.66879630638176</v>
       </c>
       <c r="F32">
-        <v>3.417943167583636</v>
+        <v>1.804728059821805</v>
       </c>
       <c r="G32">
-        <v>-4.497787773415111</v>
+        <v>-5.154927752414903</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.13662570611376</v>
       </c>
       <c r="E33">
-        <v>-21.09809002285968</v>
+        <v>-24.54456667892934</v>
       </c>
       <c r="F33">
-        <v>3.424867129845937</v>
+        <v>1.344048597197371</v>
       </c>
       <c r="G33">
-        <v>-3.112840910334246</v>
+        <v>-5.205267907885061</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.359434308813229</v>
       </c>
       <c r="E34">
-        <v>-21.12134826536307</v>
+        <v>-24.64689660608067</v>
       </c>
       <c r="F34">
-        <v>3.058674729548451</v>
+        <v>1.335023057185281</v>
       </c>
       <c r="G34">
-        <v>-2.8530425385944</v>
+        <v>-4.577797038008217</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.50712759438535</v>
       </c>
       <c r="E35">
-        <v>-20.01601568720085</v>
+        <v>-23.87454272170245</v>
       </c>
       <c r="F35">
-        <v>3.233653645027609</v>
+        <v>0.9775426231286273</v>
       </c>
       <c r="G35">
-        <v>-2.944814171488537</v>
+        <v>-5.180528201070087</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.583750696946039</v>
       </c>
       <c r="E36">
-        <v>-19.39686460697613</v>
+        <v>-23.17642411173197</v>
       </c>
       <c r="F36">
-        <v>2.954004438185227</v>
+        <v>0.8594171663078297</v>
       </c>
       <c r="G36">
-        <v>-4.397885440676524</v>
+        <v>-5.395690487303939</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-8.613498655994409</v>
       </c>
       <c r="E37">
-        <v>-19.12655093651027</v>
+        <v>-22.90525908815267</v>
       </c>
       <c r="F37">
-        <v>2.776744986187836</v>
+        <v>1.293708920969212</v>
       </c>
       <c r="G37">
-        <v>-3.804887281500112</v>
+        <v>-5.177750653362638</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-8.608718383385655</v>
       </c>
       <c r="E38">
-        <v>-19.17260098869427</v>
+        <v>-22.51657110712631</v>
       </c>
       <c r="F38">
-        <v>2.914052289056436</v>
+        <v>1.421270097634198</v>
       </c>
       <c r="G38">
-        <v>-3.761118558925408</v>
+        <v>-5.65396600809572</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.599610441568055</v>
       </c>
       <c r="E39">
-        <v>-18.89046347259438</v>
+        <v>-20.17015135699993</v>
       </c>
       <c r="F39">
-        <v>2.820197125389748</v>
+        <v>1.402443001711454</v>
       </c>
       <c r="G39">
-        <v>-3.723355165958941</v>
+        <v>-4.946247514346943</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.599470261139535</v>
       </c>
       <c r="E40">
-        <v>-18.27032518503599</v>
+        <v>-21.62688446120935</v>
       </c>
       <c r="F40">
-        <v>2.79731890973531</v>
+        <v>1.257388209504524</v>
       </c>
       <c r="G40">
-        <v>-3.157142630740773</v>
+        <v>-5.507712727261797</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.636819021684799</v>
       </c>
       <c r="E41">
-        <v>-17.60330360607619</v>
+        <v>-20.41200356832758</v>
       </c>
       <c r="F41">
-        <v>3.225790545157452</v>
+        <v>1.493102246840785</v>
       </c>
       <c r="G41">
-        <v>-3.368987750344275</v>
+        <v>-4.294245502024101</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.719741574183768</v>
       </c>
       <c r="E42">
-        <v>-16.77689785594241</v>
+        <v>-20.78283124786769</v>
       </c>
       <c r="F42">
-        <v>3.055960257609387</v>
+        <v>1.456155971539498</v>
       </c>
       <c r="G42">
-        <v>-3.775913386940411</v>
+        <v>-5.069528919683863</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.868635137629747</v>
       </c>
       <c r="E43">
-        <v>-15.64660885752392</v>
+        <v>-19.33280028518962</v>
       </c>
       <c r="F43">
-        <v>2.721883829571098</v>
+        <v>1.094420119688059</v>
       </c>
       <c r="G43">
-        <v>-3.648093223669151</v>
+        <v>-5.634721806875937</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.07891162052562</v>
       </c>
       <c r="E44">
-        <v>-15.34973115852907</v>
+        <v>-19.67520726185759</v>
       </c>
       <c r="F44">
-        <v>2.92893120613199</v>
+        <v>1.218748952579632</v>
       </c>
       <c r="G44">
-        <v>-3.541953823134577</v>
+        <v>-5.334081234818102</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.35501739185964</v>
       </c>
       <c r="E45">
-        <v>-14.8021661954176</v>
+        <v>-18.21464306863767</v>
       </c>
       <c r="F45">
-        <v>2.772587758159807</v>
+        <v>1.456314342131042</v>
       </c>
       <c r="G45">
-        <v>-3.68602545445812</v>
+        <v>-5.498376988841053</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.677158258775146</v>
       </c>
       <c r="E46">
-        <v>-15.17815633532645</v>
+        <v>-17.62950535668456</v>
       </c>
       <c r="F46">
-        <v>2.839402727026282</v>
+        <v>1.383091699130699</v>
       </c>
       <c r="G46">
-        <v>-3.554331952905912</v>
+        <v>-6.013269447109439</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.03542873494634</v>
       </c>
       <c r="E47">
-        <v>-14.39126152090961</v>
+        <v>-18.11478568829454</v>
       </c>
       <c r="F47">
-        <v>2.804485179002673</v>
+        <v>1.52112117189674</v>
       </c>
       <c r="G47">
-        <v>-3.428690128599492</v>
+        <v>-5.682287725184184</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-10.40144317922491</v>
       </c>
       <c r="E48">
-        <v>-13.04168569714369</v>
+        <v>-16.75301015555195</v>
       </c>
       <c r="F48">
-        <v>2.91033849868473</v>
+        <v>1.416531649535203</v>
       </c>
       <c r="G48">
-        <v>-4.187983611304574</v>
+        <v>-5.465192080355398</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-10.75743743146165</v>
       </c>
       <c r="E49">
-        <v>-12.61963644810282</v>
+        <v>-16.56915863931454</v>
       </c>
       <c r="F49">
-        <v>2.47041350208213</v>
+        <v>1.112224141589429</v>
       </c>
       <c r="G49">
-        <v>-3.328519641672224</v>
+        <v>-5.632738790097913</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-11.0765576919767</v>
       </c>
       <c r="E50">
-        <v>-13.1613642082184</v>
+        <v>-15.65696094910546</v>
       </c>
       <c r="F50">
-        <v>2.716046289566788</v>
+        <v>1.375895339450942</v>
       </c>
       <c r="G50">
-        <v>-4.142864186149847</v>
+        <v>-5.922146681141</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-11.34251612747659</v>
       </c>
       <c r="E51">
-        <v>-11.9277535468409</v>
+        <v>-15.7213377355985</v>
       </c>
       <c r="F51">
-        <v>2.572304389563758</v>
+        <v>1.431782737500885</v>
       </c>
       <c r="G51">
-        <v>-3.717985461094244</v>
+        <v>-6.341837781336565</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-11.53895944508294</v>
       </c>
       <c r="E52">
-        <v>-11.27600651070897</v>
+        <v>-14.49832370339895</v>
       </c>
       <c r="F52">
-        <v>2.25576750453896</v>
+        <v>1.346533431778695</v>
       </c>
       <c r="G52">
-        <v>-3.285035626013897</v>
+        <v>-6.248328112034311</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-11.65794831275346</v>
       </c>
       <c r="E53">
-        <v>-11.27185842851794</v>
+        <v>-15.30899753483007</v>
       </c>
       <c r="F53">
-        <v>2.562957357250834</v>
+        <v>1.457885378399158</v>
       </c>
       <c r="G53">
-        <v>-3.878980601214541</v>
+        <v>-5.335461732307978</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-11.69774761477103</v>
       </c>
       <c r="E54">
-        <v>-10.21416539691642</v>
+        <v>-14.48756404915672</v>
       </c>
       <c r="F54">
-        <v>2.478640854312838</v>
+        <v>1.186317822843263</v>
       </c>
       <c r="G54">
-        <v>-4.717151141938299</v>
+        <v>-6.541841079546095</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-11.66081427193996</v>
       </c>
       <c r="E55">
-        <v>-9.691846676397709</v>
+        <v>-14.84331191025129</v>
       </c>
       <c r="F55">
-        <v>2.492457104719132</v>
+        <v>1.137826331418423</v>
       </c>
       <c r="G55">
-        <v>-3.56333332622719</v>
+        <v>-5.695837788076422</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-11.55909773247327</v>
       </c>
       <c r="E56">
-        <v>-10.43630968936268</v>
+        <v>-14.78434665019742</v>
       </c>
       <c r="F56">
-        <v>2.200063816375208</v>
+        <v>1.07543148576194</v>
       </c>
       <c r="G56">
-        <v>-4.11200990172384</v>
+        <v>-6.360638369454087</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-11.40124981800552</v>
       </c>
       <c r="E57">
-        <v>-9.424145935434275</v>
+        <v>-13.63575355983992</v>
       </c>
       <c r="F57">
-        <v>2.334834022367274</v>
+        <v>1.20692183680313</v>
       </c>
       <c r="G57">
-        <v>-4.525440760304643</v>
+        <v>-5.891944574186229</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-11.2063702548837</v>
       </c>
       <c r="E58">
-        <v>-9.487141537354978</v>
+        <v>-13.77715968920344</v>
       </c>
       <c r="F58">
-        <v>2.366107463079457</v>
+        <v>1.157611569420008</v>
       </c>
       <c r="G58">
-        <v>-4.187530066565694</v>
+        <v>-7.348313146731331</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-10.98273525090266</v>
       </c>
       <c r="E59">
-        <v>-8.516123498260262</v>
+        <v>-11.71918109099562</v>
       </c>
       <c r="F59">
-        <v>2.300660816123921</v>
+        <v>0.9886095600657181</v>
       </c>
       <c r="G59">
-        <v>-4.576588688886384</v>
+        <v>-6.163995274966918</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.74924889655071</v>
       </c>
       <c r="E60">
-        <v>-8.987107437428017</v>
+        <v>-12.07572143504153</v>
       </c>
       <c r="F60">
-        <v>1.934995789896277</v>
+        <v>0.7589056866785499</v>
       </c>
       <c r="G60">
-        <v>-4.677441148194741</v>
+        <v>-6.43053060687918</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.50765590663166</v>
       </c>
       <c r="E61">
-        <v>-8.227800086665898</v>
+        <v>-12.36937938901693</v>
       </c>
       <c r="F61">
-        <v>1.797126271427696</v>
+        <v>0.6067796475591828</v>
       </c>
       <c r="G61">
-        <v>-4.611058089041275</v>
+        <v>-6.847543475733475</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.27165629084555</v>
       </c>
       <c r="E62">
-        <v>-8.570428958560244</v>
+        <v>-11.36283999980605</v>
       </c>
       <c r="F62">
-        <v>1.964748872929638</v>
+        <v>0.9626637060530736</v>
       </c>
       <c r="G62">
-        <v>-4.730184759726409</v>
+        <v>-7.169861499982457</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.03552279545871</v>
       </c>
       <c r="E63">
-        <v>-8.022592287008315</v>
+        <v>-10.36524434676031</v>
       </c>
       <c r="F63">
-        <v>1.694693756522988</v>
+        <v>0.6133852849324807</v>
       </c>
       <c r="G63">
-        <v>-4.901833235392081</v>
+        <v>-7.424591426501679</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.805688295813253</v>
       </c>
       <c r="E64">
-        <v>-8.222832350679482</v>
+        <v>-11.88526740370094</v>
       </c>
       <c r="F64">
-        <v>1.589380480558095</v>
+        <v>0.5074662414549328</v>
       </c>
       <c r="G64">
-        <v>-4.725122935596864</v>
+        <v>-8.13442204830451</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.568978746205648</v>
       </c>
       <c r="E65">
-        <v>-7.746586324714815</v>
+        <v>-10.72368664988945</v>
       </c>
       <c r="F65">
-        <v>1.681878408255252</v>
+        <v>0.0287317395415308</v>
       </c>
       <c r="G65">
-        <v>-4.817119685587671</v>
+        <v>-7.791952733357984</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.326254439232342</v>
       </c>
       <c r="E66">
-        <v>-7.168739455914054</v>
+        <v>-11.73848144721631</v>
       </c>
       <c r="F66">
-        <v>1.803673311682122</v>
+        <v>0.2488716129053603</v>
       </c>
       <c r="G66">
-        <v>-4.931495723423951</v>
+        <v>-7.094887575154583</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.061223077810292</v>
       </c>
       <c r="E67">
-        <v>-7.671395542291456</v>
+        <v>-11.16937906172436</v>
       </c>
       <c r="F67">
-        <v>1.518587242432037</v>
+        <v>0.05693754189550736</v>
       </c>
       <c r="G67">
-        <v>-4.167795904606098</v>
+        <v>-7.965498151617658</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.775084365087162</v>
       </c>
       <c r="E68">
-        <v>-7.465069209553979</v>
+        <v>-10.45624403194445</v>
       </c>
       <c r="F68">
-        <v>1.460492158335971</v>
+        <v>-0.2267429883546259</v>
       </c>
       <c r="G68">
-        <v>-4.818152575795923</v>
+        <v>-7.584861557148876</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.454822017944672</v>
       </c>
       <c r="E69">
-        <v>-7.326814898099803</v>
+        <v>-10.22856594426081</v>
       </c>
       <c r="F69">
-        <v>1.520639725298446</v>
+        <v>0.1552239147135949</v>
       </c>
       <c r="G69">
-        <v>-5.071700637557625</v>
+        <v>-6.773811005482827</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.106405268671407</v>
       </c>
       <c r="E70">
-        <v>-7.809088322968681</v>
+        <v>-10.32975016748819</v>
       </c>
       <c r="F70">
-        <v>1.297771126642314</v>
+        <v>-0.02603993769098477</v>
       </c>
       <c r="G70">
-        <v>-4.601705797892834</v>
+        <v>-6.485886238841333</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.722376342448712</v>
       </c>
       <c r="E71">
-        <v>-7.099209266000283</v>
+        <v>-10.8346523769734</v>
       </c>
       <c r="F71">
-        <v>1.397715639553867</v>
+        <v>-0.7246181599620291</v>
       </c>
       <c r="G71">
-        <v>-4.627269830547085</v>
+        <v>-7.054422777028071</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.314324068962959</v>
       </c>
       <c r="E72">
-        <v>-7.017529180323933</v>
+        <v>-11.21137160119749</v>
       </c>
       <c r="F72">
-        <v>0.8692298081598926</v>
+        <v>-0.2231202610730582</v>
       </c>
       <c r="G72">
-        <v>-4.076583753908099</v>
+        <v>-7.505461432934995</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.880167273129806</v>
       </c>
       <c r="E73">
-        <v>-8.34852920371039</v>
+        <v>-11.88822902570196</v>
       </c>
       <c r="F73">
-        <v>0.6746826223895646</v>
+        <v>-0.2752360634853818</v>
       </c>
       <c r="G73">
-        <v>-3.487323200645524</v>
+        <v>-6.631374783655684</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.435460309705397</v>
       </c>
       <c r="E74">
-        <v>-7.071241410528911</v>
+        <v>-10.24873123901696</v>
       </c>
       <c r="F74">
-        <v>1.295896018838434</v>
+        <v>-0.4975685776891373</v>
       </c>
       <c r="G74">
-        <v>-3.946370066211945</v>
+        <v>-6.486617869405513</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.980660584033977</v>
       </c>
       <c r="E75">
-        <v>-8.853001208164867</v>
+        <v>-11.57887538081597</v>
       </c>
       <c r="F75">
-        <v>0.7419346940887007</v>
+        <v>-0.2423789168577596</v>
       </c>
       <c r="G75">
-        <v>-3.700770624290034</v>
+        <v>-6.378538489184926</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.531858359228275</v>
       </c>
       <c r="E76">
-        <v>-8.789149724656715</v>
+        <v>-12.74282452653347</v>
       </c>
       <c r="F76">
-        <v>0.7773574442993348</v>
+        <v>-0.3262701947574603</v>
       </c>
       <c r="G76">
-        <v>-3.319485162895553</v>
+        <v>-6.928565767261598</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.088606120159186</v>
       </c>
       <c r="E77">
-        <v>-8.574477414323102</v>
+        <v>-11.54303250904526</v>
       </c>
       <c r="F77">
-        <v>0.583914101552068</v>
+        <v>-0.3678844432445049</v>
       </c>
       <c r="G77">
-        <v>-3.413623835850269</v>
+        <v>-5.217119660915651</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.664284004591112</v>
       </c>
       <c r="E78">
-        <v>-9.3077958527552</v>
+        <v>-13.15730669550753</v>
       </c>
       <c r="F78">
-        <v>0.7065214461135592</v>
+        <v>-1.026869225776605</v>
       </c>
       <c r="G78">
-        <v>-2.6162028001694</v>
+        <v>-5.952070702270472</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.255421418316574</v>
       </c>
       <c r="E79">
-        <v>-9.646480423788867</v>
+        <v>-13.42579086247429</v>
       </c>
       <c r="F79">
-        <v>0.7220290944375423</v>
+        <v>-0.5477158336485696</v>
       </c>
       <c r="G79">
-        <v>-2.263295335137552</v>
+        <v>-5.313155276464369</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.872177230369036</v>
       </c>
       <c r="E80">
-        <v>-10.08275360968783</v>
+        <v>-12.98183738465831</v>
       </c>
       <c r="F80">
-        <v>0.7605749127134229</v>
+        <v>-0.6276137970824898</v>
       </c>
       <c r="G80">
-        <v>-2.428925239012829</v>
+        <v>-4.840154461449919</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.510138044723381</v>
       </c>
       <c r="E81">
-        <v>-10.59945249396302</v>
+        <v>-14.15166901811178</v>
       </c>
       <c r="F81">
-        <v>0.5399567601631308</v>
+        <v>-0.7765011576047831</v>
       </c>
       <c r="G81">
-        <v>-1.946353636844347</v>
+        <v>-5.4720879467137</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.177867545617444</v>
       </c>
       <c r="E82">
-        <v>-12.02073217516639</v>
+        <v>-16.49794385706992</v>
       </c>
       <c r="F82">
-        <v>0.2537533863897024</v>
+        <v>-0.6302704637556394</v>
       </c>
       <c r="G82">
-        <v>-1.194585024150028</v>
+        <v>-4.39554488498026</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.873440215658924</v>
       </c>
       <c r="E83">
-        <v>-13.7362811543362</v>
+        <v>-14.86809172002127</v>
       </c>
       <c r="F83">
-        <v>0.4508329179188181</v>
+        <v>-0.8159449371347179</v>
       </c>
       <c r="G83">
-        <v>-1.706776077258369</v>
+        <v>-4.524394627914234</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.604983853851507</v>
       </c>
       <c r="E84">
-        <v>-13.63201304030959</v>
+        <v>-16.24234772712899</v>
       </c>
       <c r="F84">
-        <v>0.2409245766216852</v>
+        <v>-0.9506834690084752</v>
       </c>
       <c r="G84">
-        <v>-1.109606630702475</v>
+        <v>-3.862573537521913</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.373466353205365</v>
       </c>
       <c r="E85">
-        <v>-14.93666187344541</v>
+        <v>-17.46507193699205</v>
       </c>
       <c r="F85">
-        <v>0.4284804926283058</v>
+        <v>-0.9867167378495113</v>
       </c>
       <c r="G85">
-        <v>-0.8941497059156281</v>
+        <v>-4.688687071391645</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.185259661694222</v>
       </c>
       <c r="E86">
-        <v>-16.44848386395814</v>
+        <v>-18.21912625790527</v>
       </c>
       <c r="F86">
-        <v>0.5718684343592356</v>
+        <v>-1.319287853415176</v>
       </c>
       <c r="G86">
-        <v>-1.473726913475835</v>
+        <v>-3.002023708952682</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.042315240163193</v>
       </c>
       <c r="E87">
-        <v>-17.82970919256367</v>
+        <v>-18.67973093464744</v>
       </c>
       <c r="F87">
-        <v>-0.03554929986024093</v>
+        <v>-1.314794087880116</v>
       </c>
       <c r="G87">
-        <v>-0.7650582931572875</v>
+        <v>-2.452390385795183</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.948049263808742</v>
       </c>
       <c r="E88">
-        <v>-19.46353732979106</v>
+        <v>-21.14628657172331</v>
       </c>
       <c r="F88">
-        <v>0.04107593529942358</v>
+        <v>-1.322979471904065</v>
       </c>
       <c r="G88">
-        <v>-0.2391582709708237</v>
+        <v>-3.08329760194179</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.903950665824317</v>
       </c>
       <c r="E89">
-        <v>-20.47253568038811</v>
+        <v>-22.07553849504528</v>
       </c>
       <c r="F89">
-        <v>-0.3046003467165023</v>
+        <v>-0.7989454378383909</v>
       </c>
       <c r="G89">
-        <v>-0.188109658755262</v>
+        <v>-3.055651236143336</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.909065851212358</v>
       </c>
       <c r="E90">
-        <v>-20.77544077828717</v>
+        <v>-23.98179510010011</v>
       </c>
       <c r="F90">
-        <v>-0.281541588587704</v>
+        <v>-1.412049468147253</v>
       </c>
       <c r="G90">
-        <v>0.3676018260123387</v>
+        <v>-2.378611567906985</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.96290831086787</v>
       </c>
       <c r="E91">
-        <v>-23.51304822709215</v>
+        <v>-26.17523846977338</v>
       </c>
       <c r="F91">
-        <v>-0.5540332365452576</v>
+        <v>-1.602927999164465</v>
       </c>
       <c r="G91">
-        <v>0.449140562644588</v>
+        <v>-2.420542937707394</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.059708351241862</v>
       </c>
       <c r="E92">
-        <v>-25.56686515768691</v>
+        <v>-26.87288158997305</v>
       </c>
       <c r="F92">
-        <v>-0.4014384204749205</v>
+        <v>-1.65150817812057</v>
       </c>
       <c r="G92">
-        <v>0.1177681963456993</v>
+        <v>-2.87130350778902</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.197420025684858</v>
       </c>
       <c r="E93">
-        <v>-27.38627468822264</v>
+        <v>-28.66983441790474</v>
       </c>
       <c r="F93">
-        <v>-0.5203660243418881</v>
+        <v>-1.73146869793815</v>
       </c>
       <c r="G93">
-        <v>-0.1141620030445615</v>
+        <v>-2.552660189088629</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.366977499051437</v>
       </c>
       <c r="E94">
-        <v>-29.89929473285421</v>
+        <v>-31.87587853924816</v>
       </c>
       <c r="F94">
-        <v>-0.7607100259219364</v>
+        <v>-1.965299708940954</v>
       </c>
       <c r="G94">
-        <v>0.03178670759974803</v>
+        <v>-2.728910323053888</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.565026514852932</v>
       </c>
       <c r="E95">
-        <v>-32.09139767422121</v>
+        <v>-33.93510473204509</v>
       </c>
       <c r="F95">
-        <v>-1.065445134464879</v>
+        <v>-1.549865140614709</v>
       </c>
       <c r="G95">
-        <v>-0.3901158370160506</v>
+        <v>-2.602616321276231</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.783948862181036</v>
       </c>
       <c r="E96">
-        <v>-33.89146609227017</v>
+        <v>-35.18921805949231</v>
       </c>
       <c r="F96">
-        <v>-1.057992214426821</v>
+        <v>-2.190764793445449</v>
       </c>
       <c r="G96">
-        <v>-0.7780025262158378</v>
+        <v>-2.298893631321335</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.017921787840756</v>
       </c>
       <c r="E97">
-        <v>-36.21515516711506</v>
+        <v>-37.27127908247292</v>
       </c>
       <c r="F97">
-        <v>-1.390132561983486</v>
+        <v>-2.83937313481959</v>
       </c>
       <c r="G97">
-        <v>-0.9663659463092897</v>
+        <v>-2.574907055112531</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.262689785373349</v>
       </c>
       <c r="E98">
-        <v>-39.79632901830587</v>
+        <v>-39.15673187793652</v>
       </c>
       <c r="F98">
-        <v>-1.429723626163557</v>
+        <v>-2.493106130497205</v>
       </c>
       <c r="G98">
-        <v>-1.146148432364951</v>
+        <v>-4.244391996748216</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.504924494489468</v>
       </c>
       <c r="E99">
-        <v>-41.87737566310876</v>
+        <v>-41.80919722268628</v>
       </c>
       <c r="F99">
-        <v>-1.911932778855433</v>
+        <v>-2.513716479280734</v>
       </c>
       <c r="G99">
-        <v>-1.190274693857897</v>
+        <v>-2.498016324417418</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.748417070265966</v>
       </c>
       <c r="E100">
-        <v>-43.97718151148842</v>
+        <v>-44.79828894703322</v>
       </c>
       <c r="F100">
-        <v>-1.943283029304515</v>
+        <v>-2.949279157939257</v>
       </c>
       <c r="G100">
-        <v>-1.45148997908855</v>
+        <v>-4.3854576527221</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.965507261132822</v>
       </c>
       <c r="E101">
-        <v>-46.48388433487929</v>
+        <v>-45.46339045301377</v>
       </c>
       <c r="F101">
-        <v>-2.116120774385999</v>
+        <v>-2.817056342912175</v>
       </c>
       <c r="G101">
-        <v>-2.139941097798769</v>
+        <v>-4.200924533817585</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.185061005641145</v>
       </c>
       <c r="E102">
-        <v>-48.78566691671207</v>
+        <v>-48.40685100902243</v>
       </c>
       <c r="F102">
-        <v>-2.307672380417273</v>
+        <v>-3.177964708422797</v>
       </c>
       <c r="G102">
-        <v>-2.331744174707523</v>
+        <v>-4.28866392224489</v>
       </c>
     </row>
   </sheetData>
